--- a/data/all_cities_bldheight.xlsx
+++ b/data/all_cities_bldheight.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -38,190 +38,190 @@
     <t>mean_bldheight</t>
   </si>
   <si>
-    <t>澳门.xlsx</t>
-  </si>
-  <si>
-    <t>保定.xlsx</t>
-  </si>
-  <si>
-    <t>北京.xlsx</t>
-  </si>
-  <si>
-    <t>常州.xlsx</t>
-  </si>
-  <si>
-    <t>成都.xlsx</t>
-  </si>
-  <si>
-    <t>大连.xlsx</t>
-  </si>
-  <si>
-    <t>东莞.xlsx</t>
-  </si>
-  <si>
-    <t>鄂尔多斯.xlsx</t>
-  </si>
-  <si>
-    <t>佛山.xlsx</t>
-  </si>
-  <si>
-    <t>福州.xlsx</t>
-  </si>
-  <si>
-    <t>广州.xlsx</t>
-  </si>
-  <si>
-    <t>贵阳.xlsx</t>
-  </si>
-  <si>
-    <t>哈尔滨.xlsx</t>
-  </si>
-  <si>
-    <t>海口.xlsx</t>
-  </si>
-  <si>
-    <t>杭州.xlsx</t>
-  </si>
-  <si>
-    <t>合肥.xlsx</t>
-  </si>
-  <si>
-    <t>呼和浩特.xlsx</t>
-  </si>
-  <si>
-    <t>惠州.xlsx</t>
-  </si>
-  <si>
-    <t>济南.xlsx</t>
-  </si>
-  <si>
-    <t>嘉兴.xlsx</t>
-  </si>
-  <si>
-    <t>金华.xlsx</t>
-  </si>
-  <si>
-    <t>昆明.xlsx</t>
-  </si>
-  <si>
-    <t>拉萨.xlsx</t>
-  </si>
-  <si>
-    <t>兰州.xlsx</t>
-  </si>
-  <si>
-    <t>洛阳.xlsx</t>
-  </si>
-  <si>
-    <t>南昌.xlsx</t>
-  </si>
-  <si>
-    <t>南京.xlsx</t>
-  </si>
-  <si>
-    <t>南宁.xlsx</t>
-  </si>
-  <si>
-    <t>南通.xlsx</t>
-  </si>
-  <si>
-    <t>宁波.xlsx</t>
-  </si>
-  <si>
-    <t>青岛.xlsx</t>
-  </si>
-  <si>
-    <t>泉州.xlsx</t>
-  </si>
-  <si>
-    <t>三亚.xlsx</t>
-  </si>
-  <si>
-    <t>厦门.xlsx</t>
-  </si>
-  <si>
-    <t>汕头.xlsx</t>
-  </si>
-  <si>
-    <t>上海.xlsx</t>
-  </si>
-  <si>
-    <t>绍兴.xlsx</t>
-  </si>
-  <si>
-    <t>深圳.xlsx</t>
-  </si>
-  <si>
-    <t>沈阳.xlsx</t>
-  </si>
-  <si>
-    <t>石家庄.xlsx</t>
-  </si>
-  <si>
-    <t>苏州.xlsx</t>
-  </si>
-  <si>
-    <t>台州.xlsx</t>
-  </si>
-  <si>
-    <t>太原.xlsx</t>
-  </si>
-  <si>
-    <t>唐山.xlsx</t>
-  </si>
-  <si>
-    <t>天津.xlsx</t>
-  </si>
-  <si>
-    <t>温州.xlsx</t>
-  </si>
-  <si>
-    <t>无锡.xlsx</t>
-  </si>
-  <si>
-    <t>芜湖.xlsx</t>
-  </si>
-  <si>
-    <t>武汉.xlsx</t>
-  </si>
-  <si>
-    <t>西安.xlsx</t>
-  </si>
-  <si>
-    <t>西宁.xlsx</t>
-  </si>
-  <si>
-    <t>香港.xlsx</t>
-  </si>
-  <si>
-    <t>徐州.xlsx</t>
-  </si>
-  <si>
-    <t>烟台.xlsx</t>
-  </si>
-  <si>
-    <t>扬州.xlsx</t>
-  </si>
-  <si>
-    <t>银川.xlsx</t>
-  </si>
-  <si>
-    <t>长春.xlsx</t>
-  </si>
-  <si>
-    <t>长沙.xlsx</t>
-  </si>
-  <si>
-    <t>郑州.xlsx</t>
-  </si>
-  <si>
-    <t>中山.xlsx</t>
-  </si>
-  <si>
-    <t>重庆.xlsx</t>
-  </si>
-  <si>
-    <t>珠海.xlsx</t>
+    <t>Macao</t>
+  </si>
+  <si>
+    <t>Baoing</t>
+  </si>
+  <si>
+    <t>Beijing</t>
+  </si>
+  <si>
+    <t>Changzhou</t>
+  </si>
+  <si>
+    <t>Chengdu</t>
+  </si>
+  <si>
+    <t>Dalian</t>
+  </si>
+  <si>
+    <t>Dongguan</t>
+  </si>
+  <si>
+    <t>Ordos</t>
+  </si>
+  <si>
+    <t>Foshan</t>
+  </si>
+  <si>
+    <t>Fuzhou</t>
+  </si>
+  <si>
+    <t>Guangzhou</t>
+  </si>
+  <si>
+    <t>Guiyang</t>
+  </si>
+  <si>
+    <t>Harbin</t>
+  </si>
+  <si>
+    <t>Haikou</t>
+  </si>
+  <si>
+    <t>Hangzhou</t>
+  </si>
+  <si>
+    <t>Hefei</t>
+  </si>
+  <si>
+    <t>Hohhot</t>
+  </si>
+  <si>
+    <t>Huizhou</t>
+  </si>
+  <si>
+    <t>Jinan</t>
+  </si>
+  <si>
+    <t>Jiaxing</t>
+  </si>
+  <si>
+    <t>Jinhua</t>
+  </si>
+  <si>
+    <t>Kunming</t>
+  </si>
+  <si>
+    <t>Lhasa</t>
+  </si>
+  <si>
+    <t>Lanzhou</t>
+  </si>
+  <si>
+    <t>Luoyang</t>
+  </si>
+  <si>
+    <t>Nanchang</t>
+  </si>
+  <si>
+    <t>Nanjing</t>
+  </si>
+  <si>
+    <t>Nanning</t>
+  </si>
+  <si>
+    <t>Nantong</t>
+  </si>
+  <si>
+    <t>Ningbo</t>
+  </si>
+  <si>
+    <t>Qingdao</t>
+  </si>
+  <si>
+    <t>Quanzhou</t>
+  </si>
+  <si>
+    <t>Sanya</t>
+  </si>
+  <si>
+    <t>Xiamen</t>
+  </si>
+  <si>
+    <t>Shantou</t>
+  </si>
+  <si>
+    <t>Shanghai</t>
+  </si>
+  <si>
+    <t>Shaoxing</t>
+  </si>
+  <si>
+    <t>Shenzhen</t>
+  </si>
+  <si>
+    <t>Shenyang</t>
+  </si>
+  <si>
+    <t>Shijiazhuang</t>
+  </si>
+  <si>
+    <t>Suzhou</t>
+  </si>
+  <si>
+    <t>Taizhou</t>
+  </si>
+  <si>
+    <t>Taiyuan</t>
+  </si>
+  <si>
+    <t>Tangshan</t>
+  </si>
+  <si>
+    <t>Tianjin</t>
+  </si>
+  <si>
+    <t>Wenzhou</t>
+  </si>
+  <si>
+    <t>Wuxi</t>
+  </si>
+  <si>
+    <t>Wuhu</t>
+  </si>
+  <si>
+    <t>Wuhan</t>
+  </si>
+  <si>
+    <t>Xi'an</t>
+  </si>
+  <si>
+    <t>Xining</t>
+  </si>
+  <si>
+    <t>Hong Kong</t>
+  </si>
+  <si>
+    <t>Xuzhou</t>
+  </si>
+  <si>
+    <t>Yantai</t>
+  </si>
+  <si>
+    <t>Yangzhou</t>
+  </si>
+  <si>
+    <t>Yinchuan</t>
+  </si>
+  <si>
+    <t>Changchun</t>
+  </si>
+  <si>
+    <t>Changsha</t>
+  </si>
+  <si>
+    <t>Zhengzhou</t>
+  </si>
+  <si>
+    <t>Zhongshan</t>
+  </si>
+  <si>
+    <t>Chongqing</t>
+  </si>
+  <si>
+    <t>Zhuhai</t>
   </si>
 </sst>
 </file>
@@ -246,16 +246,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -720,19 +718,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -741,7 +739,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -865,11 +863,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1216,7 +1216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="12.8181818181818"/>
@@ -1231,500 +1231,504 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>16.9613626479488</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>10.3544207391292</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>11.2680535468863</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>13.4765391317779</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>18.1633513147324</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>14.672804212272</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>12.5879726954362</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>8.7322078501586</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>12.4353412291532</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>16.5222488921794</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>11.8312248891736</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>18.1712214513717</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>16.0948027943748</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>9.4214206774742</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>17.6196890166058</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>19.2145123960885</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>10.8494004712015</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="3">
         <v>17.54538773588</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>15.9634264172169</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>14.4653165209623</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="3">
         <v>12.0241947551803</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="3">
         <v>22.0112063877442</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="3">
         <v>6.27886191182937</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="3">
         <v>9.90672761827395</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="3">
         <v>16.027862817237</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" t="s">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="3">
         <v>14.1989464131358</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="3">
         <v>14.1464561851393</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" t="s">
+      <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="3">
         <v>16.7334187426786</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" t="s">
+      <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="3">
         <v>15.6158224325709</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" t="s">
+      <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="3">
         <v>15.4434295766298</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" t="s">
+      <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="3">
         <v>15.4238963956932</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s">
+      <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="3">
         <v>16.160401097193</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s">
+      <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="3">
         <v>8.5490709381101</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
+      <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="3">
         <v>12.9715409133288</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" t="s">
+      <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="3">
         <v>10.5441909179604</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" t="s">
+      <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="3">
         <v>14.5173034193708</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" t="s">
+      <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="3">
         <v>15.6868967071272</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" t="s">
+      <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="3">
         <v>18.6375877247282</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" t="s">
+      <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="3">
         <v>12.104733753454</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" t="s">
+      <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="3">
         <v>14.955266455637</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" t="s">
+      <c r="A42" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="3">
         <v>13.1463772304273</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="3">
         <v>14.1396842185133</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="3">
         <v>10.014937991461</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="3">
         <v>9.07575057231199</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="3">
         <v>12.1343715151205</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="3">
         <v>11.9120767149045</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" t="s">
+      <c r="A48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="3">
         <v>13.4381081133403</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" t="s">
+      <c r="A49" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="3">
         <v>10.8392315462783</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" t="s">
+      <c r="A50" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="3">
         <v>14.3377755400205</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" t="s">
+      <c r="A51" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="3">
         <v>16.3630389435514</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" t="s">
+      <c r="A52" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="3">
         <v>11.6903931408006</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" t="s">
+      <c r="A53" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="3">
         <v>25.3333178200339</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" t="s">
+      <c r="A54" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="3">
         <v>12.3728124390798</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" t="s">
+      <c r="A55" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="3">
         <v>6.15783414885029</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" t="s">
+      <c r="A56" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="3">
         <v>9.49371400684831</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" t="s">
+      <c r="A57" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="3">
         <v>12.0908638939773</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" t="s">
+      <c r="A58" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="3">
         <v>11.784399551599</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" t="s">
+      <c r="A59" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="3">
         <v>19.2126832624202</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" t="s">
+      <c r="A60" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="3">
         <v>14.871645711551</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" t="s">
+      <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="3">
         <v>11.4941579514991</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" t="s">
+      <c r="A62" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="3">
         <v>19.955139145294</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" t="s">
+      <c r="A63" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="3">
         <v>15.2443443224848</v>
       </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A2:B63">
